--- a/Tools/Config/Datas/BuffSetting.xlsx
+++ b/Tools/Config/Datas/BuffSetting.xlsx
@@ -851,14 +851,14 @@
 未来不够后续拓展</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>admin:
 0为不能叠加
 1为能叠加</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>admin:
 0为不处理
@@ -868,13 +868,13 @@
 4.每层独立时间（这个未来实现）</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>admin:
 一个buff只能配置一个控制类修饰器，多个只会生效第一个，为了提高运行效率！！！</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>admin:
 -1代表无限时长</t>
@@ -1145,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col width="24.5833333333333" customWidth="1" min="3" max="3"/>
@@ -1153,7 +1153,7 @@
     <col width="16.75" customWidth="1" min="5" max="5"/>
     <col width="17.25" customWidth="1" min="6" max="6"/>
     <col width="26.75" customWidth="1" min="7" max="7"/>
-    <col width="31.75" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="15.75" customWidth="1" min="9" max="9"/>
     <col width="12.3333333333333" customWidth="1" min="10" max="10"/>
     <col width="10.75" customWidth="1" min="11" max="11"/>
@@ -1204,82 +1204,87 @@
           <t>BuffTag</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>GrantedTags</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>StatusSlot</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>CanStack</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>MaxLevel</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>RepeatedAddition</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>BuffModifyList</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="O1" s="13" t="inlineStr">
         <is>
           <t>BaseDuration</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>BaseTimes</t>
         </is>
       </c>
-      <c r="P1" s="14" t="inlineStr">
+      <c r="Q1" s="14" t="inlineStr">
         <is>
           <t>IsAddPoint</t>
         </is>
       </c>
-      <c r="Q1" s="14" t="inlineStr">
+      <c r="R1" s="14" t="inlineStr">
         <is>
           <t>ActionPointType</t>
         </is>
       </c>
-      <c r="R1" s="14" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
         <is>
           <t>CDTime</t>
         </is>
       </c>
-      <c r="S1" s="14" t="inlineStr">
+      <c r="T1" s="14" t="inlineStr">
         <is>
           <t>DelayTime</t>
         </is>
       </c>
-      <c r="T1" s="14" t="inlineStr">
+      <c r="U1" s="14" t="inlineStr">
         <is>
           <t>IntervalTime</t>
         </is>
       </c>
-      <c r="U1" s="14" t="inlineStr">
+      <c r="V1" s="14" t="inlineStr">
         <is>
           <t>TriggerFormula</t>
         </is>
       </c>
-      <c r="V1" s="15" t="inlineStr">
+      <c r="W1" s="15" t="inlineStr">
         <is>
           <t>RemoveActionPointType</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
@@ -1297,21 +1302,21 @@
       <c r="E2" s="17" t="n"/>
       <c r="F2" s="17" t="n"/>
       <c r="G2" s="17" t="n"/>
-      <c r="H2" s="17" t="n"/>
       <c r="I2" s="17" t="n"/>
-      <c r="J2" s="1" t="n"/>
+      <c r="J2" s="17" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
-      <c r="M2" s="18" t="n"/>
-      <c r="N2" s="17" t="n"/>
-      <c r="O2" s="18" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="17" t="n"/>
       <c r="P2" s="18" t="n"/>
       <c r="Q2" s="18" t="n"/>
-      <c r="R2" s="17" t="n"/>
-      <c r="S2" s="1" t="n"/>
+      <c r="R2" s="18" t="n"/>
+      <c r="S2" s="17" t="n"/>
       <c r="T2" s="1" t="n"/>
       <c r="U2" s="1" t="n"/>
       <c r="V2" s="1" t="n"/>
+      <c r="W2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1349,82 +1354,87 @@
           <t>(list#sep=|),string</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(list#sep=|),string</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>(list#sep=|),int</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="P3" s="14" t="inlineStr">
+      <c r="Q3" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q3" s="14" t="inlineStr">
+      <c r="R3" s="14" t="inlineStr">
         <is>
           <t>ActionPointType</t>
         </is>
       </c>
-      <c r="R3" s="14" t="inlineStr">
+      <c r="S3" s="14" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="S3" s="14" t="inlineStr">
+      <c r="T3" s="14" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="T3" s="14" t="inlineStr">
+      <c r="U3" s="14" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="V3" s="14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="V3" s="15" t="inlineStr">
+      <c r="W3" s="15" t="inlineStr">
         <is>
           <t>ActionPointType</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1463,85 +1473,90 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Buff标签</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+          <t>Asset标签（描述这条Buff）</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Granted标签（角色状态 State.*）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Buff描述</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>显示在状态栏</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>能否叠加</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>最大层数</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>重复添加时的处理</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>Buff效果列表</t>
         </is>
       </c>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>Buff默认时长</t>
         </is>
       </c>
-      <c r="O4" s="13" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>Buff默认次数</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>是否加入时触发</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>Buff触发点</t>
         </is>
       </c>
-      <c r="R4" s="14" t="inlineStr">
+      <c r="S4" s="14" t="inlineStr">
         <is>
           <t>冷却时间</t>
         </is>
       </c>
-      <c r="S4" s="14" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>延迟触发时间</t>
         </is>
       </c>
-      <c r="T4" s="14" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>间隔触发时间</t>
         </is>
       </c>
-      <c r="U4" s="14" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>Buff触发条件判断</t>
         </is>
       </c>
-      <c r="V4" s="15" t="inlineStr">
+      <c r="W4" s="15" t="inlineStr">
         <is>
           <t>Buff移除触发点</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Buff优先级</t>
         </is>
@@ -1555,39 +1570,49 @@
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>极性Debuff/Buff、Bind.*、Caster.KeepFirst、Outro。不进角色容器</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>State.Freeze/异常/Forbid。禁止写 Buff.Debuff/Bind/Caster/Outro</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="n"/>
-      <c r="N5" t="inlineStr">
+      <c r="K5" s="7" t="n"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>单位为秒</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1为是，其他为否</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>单位为秒</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>单位为秒</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>单位为秒</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>写表达式，#开头代表方法名</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>越大越先触发；同值按添加先后。默认0</t>
         </is>
@@ -1601,9 +1626,19 @@
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>对齐GAS AssetTags；一律Buff.开头。净化/生命周期/互斥读这里</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>对齐GAS GrantedTags；HasTag认容器。前缀State与Asset的Buff区分</t>
+        </is>
+      </c>
       <c r="J6" s="7" t="n"/>
-      <c r="U6" t="inlineStr">
+      <c r="K6" s="7" t="n"/>
+      <c r="V6" t="inlineStr">
         <is>
           <t>这里是给触发器和时间触发判断的</t>
         </is>
@@ -1629,30 +1664,30 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Buff.Dizziness</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>State.Dizziness</t>
+        </is>
       </c>
       <c r="J7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="N7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1676,30 +1711,30 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Buff.Silence</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>State.Silence</t>
+        </is>
       </c>
       <c r="J8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="N8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1723,30 +1758,30 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Buff.Weak</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>State.Weak</t>
+        </is>
       </c>
       <c r="J9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="N9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1770,30 +1805,30 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Buff.Fire.Normal</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>State.Fire.Normal</t>
+        </is>
       </c>
       <c r="J10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="9" t="n">
+      <c r="K10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>0.5</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1817,35 +1852,35 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Buff.Fire.Hight</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>State.Fire.Hight</t>
+        </is>
       </c>
       <c r="J11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="9" t="n">
+      <c r="K11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>0.5</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>#CheckIsHadFireBigBuff</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1869,28 +1904,28 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>0.5</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1914,32 +1949,32 @@
       <c r="F13" t="n">
         <v>10</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>造成灼烧与中毒效果</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>4|6</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>0.5</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1963,25 +1998,25 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="N14" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>0.5</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2005,35 +2040,35 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>下一次普通攻击最终伤害提升</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>PreCauseDamage</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>0.5</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2057,37 +2092,37 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>全伤害提升</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-1</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>PostReceiveDamage</t>
         </is>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2111,14 +2146,11 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>普攻或大招主轴结束后给自己挂 5 秒加攻；被动伤害不会走施法点</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -2126,31 +2158,34 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>4</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="N17" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>PostSpell</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>#IsNormalOrUltimateSpell</t>
         </is>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2174,36 +2209,36 @@
       <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>攻击力提升 20%，持续 5 秒，重复获得时刷新时间</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="N18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2227,14 +2262,11 @@
       <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>主动技能真实命中后给敌方挂点燃；Buff 伤害不会触发</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
@@ -2242,31 +2274,34 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>4</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>23</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>PostCauseDamage</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>#IsActiveSkillHit</t>
         </is>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2290,44 +2325,44 @@
       <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Buff.Fire.Ignite</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>State.Fire.Ignite</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>每秒造成 50 点火属性伤害，持续 5 秒，重复施加刷新时间</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>22</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>5</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2353,39 +2388,44 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buff.Freeze|Buff.Debuff</t>
+          <t>Buff.Debuff</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>State.Freeze</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>停动画与位移（实体钟=0），点燃跳伤仍走世界钟</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>24</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2411,39 +2451,44 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buff.Freeze|Buff.Debuff</t>
+          <t>Buff.Debuff</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>State.Freeze</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>8 秒冻结，方便看冰壳；点燃/霜蚀仍走世界钟</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>24</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>8</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2472,39 +2517,39 @@
           <t>Buff.Debuff</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>每秒 40 点冰伤，持续 6 秒。冻结中应继续跳（世界钟）</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>25</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>6</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2533,36 +2578,36 @@
           <t>Buff.Buff</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>吸收 400 点伤害，持续 10 秒。可与冻结叠测</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>26</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>10</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2591,36 +2636,425 @@
           <t>Buff.Buff</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>挂在攻击者：打带 Buff.Freeze 的目标最终伤害 +50%，持续 15 秒</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>挂在攻击者：打带 State.Freeze 的目标最终伤害 +50%，持续 15 秒</t>
+        </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>27</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>15</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>32001</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>光噪</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>State.Spectro.Frazzle</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>每秒按层跳冰伤（单层20），跳完减1层。重复施加叠层并刷新。外部打爆走 TryConsume。</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>28</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>32002</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>风蚀</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>State.Aero.Erosion</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>每秒按层跳物理伤（单层15），跳伤不掉层。重复施加叠层并刷新。</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>32003</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>电磁</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>32</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>State.Electro.Flare</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>每秒按层跳电伤（单层10），跳完层数减半；期间按层减攻5%。重复施加叠层并刷新。</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>30|31</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>32010</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>命中上光噪-触发器</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TriggerBuff</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>主动技能真实命中后给敌方挂光噪；Buff 伤害不会触发</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>32</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>PostCauseDamage</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>#IsActiveSkillHit</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>32020</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>对光噪增伤</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>16</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Buff.Buff</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>挂在攻击者：打带 State.Spectro.Frazzle 的目标最终伤害 +50%，持续 15 秒</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>15</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>32100</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>死亡爆炸</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TimeBuff|TriggerBuff</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>33</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>到期/手动卸不跳。持有者死亡时跳 80 点火伤。公式 #IsRemoveReasonDeath。</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>34</v>
+      </c>
+      <c r="O31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>PreRemoveStatus</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>#IsRemoveReasonDeath</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2641,7 +3075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66666666666667" defaultRowHeight="26" customHeight="1"/>
   <cols>
     <col width="17.9166666666667" customWidth="1" min="2" max="2"/>
@@ -2839,7 +3273,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Buff.MoveForbid|Buff.SkillForbid</t>
+          <t>State.MoveForbid|State.SkillForbid</t>
         </is>
       </c>
     </row>
@@ -2854,7 +3288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Buff.SkillForbid</t>
+          <t>State.SkillForbid</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3897,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Buff.MoveForbid|Buff.SkillForbid|Buff.Freeze</t>
+          <t>State.MoveForbid|State.SkillForbid|State.Freeze</t>
         </is>
       </c>
     </row>
@@ -3615,8 +4049,404 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Buff.Freeze</t>
-        </is>
+          <t>State.Freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>光噪跳伤 单层值×层数</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>单层固定值</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TickStackPolicy 1=减1层</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>风蚀跳伤 单层值×层数</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>单层固定值</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TickStackPolicy 0=不掉层</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>29</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>电磁跳伤 单层值×层数</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>单层固定值</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TickStackPolicy 2=减半层</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>30</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>电磁减攻 单层-5% 叠层重算</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>AttributeType</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>ModifyType</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>ApplySide</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>单层数值</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>31</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PlayerModify</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>命中上光噪</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>BuffId</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>32</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BuffAddStatus</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>32001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>对光噪目标增伤</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>FilterType=5 目标Tag</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>ApplySide</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>百分点</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>目标 Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>33</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ActionModify</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>State.Spectro.Frazzle</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>死亡爆炸 仅 PreRemoveStatus+#IsRemoveReasonDeath</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>34</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
